--- a/website/static/playground-samples/sample-template-ko.xlsx
+++ b/website/static/playground-samples/sample-template-ko.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="_config" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="__config__" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="갱신 리포트" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
@@ -41,7 +41,7 @@
     <t>거래처 갱신 파이프라인</t>
   </si>
   <si>
-    <t>운영자가 raw.xlsx 와 이 템플릿을 업로드합니다. 규칙은 _config 시트에 보관됩니다.</t>
+    <t>운영자가 raw.xlsx 와 이 템플릿을 업로드합니다. 규칙은 __config__ 시트에 보관됩니다.</t>
   </si>
   <si>
     <t>거래처 수</t>
